--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/28,07,26 Останкино СЫРЫ/дв 28,07,26 лгрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/28,07,26 Останкино СЫРЫ/дв 28,07,26 лгрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\28,07,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A22E3B-EDC2-4CC7-9FB5-2671BB2679B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF7A33F-070D-4208-A5D4-47259E6E15A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -268,12 +268,6 @@
     <t>нужно увеличить продажи / плюс 320кг пересчет (25,07,26)</t>
   </si>
   <si>
-    <t>175шт в уценку (24,07,26)</t>
-  </si>
-  <si>
-    <t>145шт в уценку (24,07,26)</t>
-  </si>
-  <si>
     <t>400шт в уценку (24,07,26)</t>
   </si>
   <si>
@@ -296,6 +290,12 @@
   </si>
   <si>
     <t>03,08,</t>
+  </si>
+  <si>
+    <t>30,07,26 - нет на заводе / 175шт в уценку (24,07,26)</t>
+  </si>
+  <si>
+    <t>30,07,26 - нет на заводе / 145шт в уценку (24,07,26)</t>
   </si>
 </sst>
 </file>
@@ -414,7 +414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -435,6 +435,7 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -916,13 +917,13 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>16</v>
@@ -1006,10 +1007,10 @@
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -1023,7 +1024,7 @@
         <v>25</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>26</v>
@@ -1726,7 +1727,7 @@
       <c r="Q11" s="5">
         <v>40</v>
       </c>
-      <c r="R11" s="5">
+      <c r="R11" s="15">
         <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
         <v>36</v>
       </c>
@@ -1766,8 +1767,8 @@
       <c r="AD11" s="1">
         <v>0</v>
       </c>
-      <c r="AE11" s="12" t="s">
-        <v>78</v>
+      <c r="AE11" s="20" t="s">
+        <v>86</v>
       </c>
       <c r="AF11" s="1">
         <f t="shared" ref="AF11:AF19" si="6">G11*Q11</f>
@@ -1835,7 +1836,7 @@
       <c r="Q12" s="5">
         <v>20</v>
       </c>
-      <c r="R12" s="5">
+      <c r="R12" s="15">
         <f>VLOOKUP(A12,заказ!A:B,2,0)</f>
         <v>24</v>
       </c>
@@ -1875,8 +1876,8 @@
       <c r="AD12" s="1">
         <v>0</v>
       </c>
-      <c r="AE12" s="12" t="s">
-        <v>79</v>
+      <c r="AE12" s="20" t="s">
+        <v>87</v>
       </c>
       <c r="AF12" s="1">
         <f t="shared" si="6"/>
@@ -2797,7 +2798,7 @@
       </c>
       <c r="R21" s="5"/>
       <c r="S21" s="18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T21" s="1">
         <f t="shared" si="4"/>
@@ -2905,7 +2906,7 @@
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T22" s="1">
         <f t="shared" si="4"/>
@@ -2943,7 +2944,7 @@
         <v>4.8</v>
       </c>
       <c r="AE22" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF22" s="1">
         <f t="shared" si="8"/>
